--- a/plantilla_skus_presentaciones.xlsx
+++ b/plantilla_skus_presentaciones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plantilla" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Plantilla" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -543,65 +543,70 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>tamano</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>grado</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>marca</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>gtin</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>plu</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>cajas_por_tarima</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>patron_estiba</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>temperatura_c</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>vida_anaquel_dias</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>es_reempaque</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>costo_caja_ref</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>precio_caja_ref</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>estado</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>nota</t>
         </is>
@@ -639,49 +644,50 @@
           <t>6–9</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Plein</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>10841234500019</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="n">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>8x10</t>
         </is>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="O2" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="P2" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -715,49 +721,50 @@
           <t>9–12</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Plein</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>10841234500033</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="n">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="n">
         <v>96</v>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>9x11</t>
         </is>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="O3" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="P3" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr"/>
       <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -770,7 +777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -792,6 +799,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -931,7 +939,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>grado</t>
+          <t>tamano</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -941,14 +949,14 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Ej. 1, 2, Fancy.</t>
+          <t>Tamaño de la presentación, si aplica (ej. Chico/Mediano/Grande). Opcional.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>grado</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -958,14 +966,14 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Marca del empaque.</t>
+          <t>Ej. 1, 2, Fancy.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>gtin</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -975,14 +983,14 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>GTIN de 14 dígitos (etiqueta PTI). Se asigna por producto+variedad+tamaño+empaque.</t>
+          <t>Marca del empaque.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>plu</t>
+          <t>gtin</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -992,14 +1000,14 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Código PLU si aplica.</t>
+          <t>GTIN de 14 dígitos (etiqueta PTI). Se asigna por producto+variedad+tamaño+empaque.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>cajas_por_tarima</t>
+          <t>plu</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1009,14 +1017,14 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Número. Automatiza pedidos: pallets × este número = cajas.</t>
+          <t>Código PLU si aplica.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>patron_estiba</t>
+          <t>cajas_por_tarima</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -1026,14 +1034,14 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Ti x Hi. Ej. 8x10 (8 cajas por cama, 10 camas).</t>
+          <t>Número. Automatiza pedidos: pallets × este número = cajas.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>temperatura_c</t>
+          <t>patron_estiba</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -1043,14 +1051,14 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Temperatura de transporte en °C.</t>
+          <t>Ti x Hi. Ej. 8x10 (8 cajas por cama, 10 camas).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>vida_anaquel_dias</t>
+          <t>temperatura_c</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -1060,14 +1068,14 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Vida de anaquel en días.</t>
+          <t>Temperatura de transporte en °C.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>es_reempaque</t>
+          <t>vida_anaquel_dias</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1077,14 +1085,14 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Sí / No.</t>
+          <t>Vida de anaquel en días.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>costo_caja_ref</t>
+          <t>es_reempaque</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -1094,14 +1102,14 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Costo de referencia por caja (opcional).</t>
+          <t>Sí / No.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>precio_caja_ref</t>
+          <t>costo_caja_ref</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1111,14 +1119,14 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Precio de referencia por caja (opcional).</t>
+          <t>Costo de referencia por caja (opcional).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>estado</t>
+          <t>precio_caja_ref</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -1128,22 +1136,39 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Activo / Inactivo. Vacío = Activo.</t>
+          <t>Precio de referencia por caja (opcional).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
+          <t>estado</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Activo / Inactivo. Vacío = Activo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
           <t>nota</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>Observaciones libres.</t>
         </is>
